--- a/data/nzd0455/nzd0455.xlsx
+++ b/data/nzd0455/nzd0455.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W378"/>
+  <dimension ref="A1:W379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28798,6 +28798,81 @@
         <v>358.7</v>
       </c>
       <c r="W378" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:25:59+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>399.7</v>
+      </c>
+      <c r="C379" t="n">
+        <v>358.09</v>
+      </c>
+      <c r="D379" t="n">
+        <v>356.29</v>
+      </c>
+      <c r="E379" t="n">
+        <v>363.44</v>
+      </c>
+      <c r="F379" t="n">
+        <v>366.97</v>
+      </c>
+      <c r="G379" t="n">
+        <v>374.21</v>
+      </c>
+      <c r="H379" t="n">
+        <v>373.73</v>
+      </c>
+      <c r="I379" t="n">
+        <v>373.88</v>
+      </c>
+      <c r="J379" t="n">
+        <v>374.06</v>
+      </c>
+      <c r="K379" t="n">
+        <v>375.62</v>
+      </c>
+      <c r="L379" t="n">
+        <v>372.09</v>
+      </c>
+      <c r="M379" t="n">
+        <v>368.41</v>
+      </c>
+      <c r="N379" t="n">
+        <v>363.88</v>
+      </c>
+      <c r="O379" t="n">
+        <v>361.49</v>
+      </c>
+      <c r="P379" t="n">
+        <v>357.9</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>357.67</v>
+      </c>
+      <c r="R379" t="n">
+        <v>349.14</v>
+      </c>
+      <c r="S379" t="n">
+        <v>350.68</v>
+      </c>
+      <c r="T379" t="n">
+        <v>345.94</v>
+      </c>
+      <c r="U379" t="n">
+        <v>358.83</v>
+      </c>
+      <c r="V379" t="n">
+        <v>357.56</v>
+      </c>
+      <c r="W379" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -28814,7 +28889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B390"/>
+  <dimension ref="A1:B391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32717,6 +32792,16 @@
       </c>
       <c r="B390" t="n">
         <v>-0.65</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>-0.23</v>
       </c>
     </row>
   </sheetData>
@@ -32885,28 +32970,28 @@
         <v>0.0326</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2602145534448707</v>
+        <v>0.2682588521546788</v>
       </c>
       <c r="J2" t="n">
+        <v>378</v>
+      </c>
+      <c r="K2" t="n">
         <v>377</v>
       </c>
-      <c r="K2" t="n">
-        <v>376</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.03010740029741121</v>
+        <v>0.03194682539132732</v>
       </c>
       <c r="M2" t="n">
-        <v>7.793657635379899</v>
+        <v>7.808497364462704</v>
       </c>
       <c r="N2" t="n">
-        <v>118.2335315343738</v>
+        <v>118.5459665455126</v>
       </c>
       <c r="O2" t="n">
-        <v>10.8735243382435</v>
+        <v>10.88788163719245</v>
       </c>
       <c r="P2" t="n">
-        <v>377.2659759203661</v>
+        <v>377.1763260577554</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32963,28 +33048,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4683183567848612</v>
+        <v>0.4704732974091894</v>
       </c>
       <c r="J3" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K3" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2633370561735384</v>
+        <v>0.265950214638611</v>
       </c>
       <c r="M3" t="n">
-        <v>4.434951579979707</v>
+        <v>4.434869385972249</v>
       </c>
       <c r="N3" t="n">
-        <v>33.36835783329539</v>
+        <v>33.3251847393078</v>
       </c>
       <c r="O3" t="n">
-        <v>5.776535106211629</v>
+        <v>5.772796959820067</v>
       </c>
       <c r="P3" t="n">
-        <v>341.3374481959593</v>
+        <v>341.313502885175</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33041,28 +33126,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7300381567086365</v>
+        <v>0.7308406736621839</v>
       </c>
       <c r="J4" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K4" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4372090853350905</v>
+        <v>0.4390873357104556</v>
       </c>
       <c r="M4" t="n">
-        <v>4.75710873348378</v>
+        <v>4.748797513193799</v>
       </c>
       <c r="N4" t="n">
-        <v>37.31166617495717</v>
+        <v>37.21921329074004</v>
       </c>
       <c r="O4" t="n">
-        <v>6.108327608679578</v>
+        <v>6.100755141024759</v>
       </c>
       <c r="P4" t="n">
-        <v>335.0906412320443</v>
+        <v>335.0817238086846</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33119,28 +33204,28 @@
         <v>0.0653</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7485303472519866</v>
+        <v>0.7493571185596206</v>
       </c>
       <c r="J5" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K5" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5018146024040783</v>
+        <v>0.5037116201637774</v>
       </c>
       <c r="M5" t="n">
-        <v>4.197082047931558</v>
+        <v>4.190441990944308</v>
       </c>
       <c r="N5" t="n">
-        <v>30.25256114761522</v>
+        <v>30.17916695974646</v>
       </c>
       <c r="O5" t="n">
-        <v>5.50023282667336</v>
+        <v>5.493556858697874</v>
       </c>
       <c r="P5" t="n">
-        <v>341.6986929700111</v>
+        <v>341.6895060366518</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33197,28 +33282,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.791425673346508</v>
+        <v>0.7909881419992849</v>
       </c>
       <c r="J6" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K6" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4739678205920473</v>
+        <v>0.4750762342178545</v>
       </c>
       <c r="M6" t="n">
-        <v>4.51719165223773</v>
+        <v>4.507279818554358</v>
       </c>
       <c r="N6" t="n">
-        <v>37.80762076879954</v>
+        <v>37.70945992321698</v>
       </c>
       <c r="O6" t="n">
-        <v>6.148790187410816</v>
+        <v>6.140802872851154</v>
       </c>
       <c r="P6" t="n">
-        <v>346.5052786659073</v>
+        <v>346.5101404351685</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33275,28 +33360,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>0.633917655983401</v>
+        <v>0.6340286327921212</v>
       </c>
       <c r="J7" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K7" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L7" t="n">
-        <v>0.486086441256667</v>
+        <v>0.4875717586585796</v>
       </c>
       <c r="M7" t="n">
-        <v>3.653186886315267</v>
+        <v>3.644194277934217</v>
       </c>
       <c r="N7" t="n">
-        <v>23.10669801284001</v>
+        <v>23.04568880083293</v>
       </c>
       <c r="O7" t="n">
-        <v>4.806942688740943</v>
+        <v>4.800592546845954</v>
       </c>
       <c r="P7" t="n">
-        <v>356.9348374090914</v>
+        <v>356.9336042548483</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33353,28 +33438,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6428296630063369</v>
+        <v>0.6436118469703471</v>
       </c>
       <c r="J8" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K8" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L8" t="n">
-        <v>0.442471842509105</v>
+        <v>0.4444023649242876</v>
       </c>
       <c r="M8" t="n">
-        <v>4.082265671393069</v>
+        <v>4.076028340683804</v>
       </c>
       <c r="N8" t="n">
-        <v>28.3183932575314</v>
+        <v>28.24941914465799</v>
       </c>
       <c r="O8" t="n">
-        <v>5.321502913419422</v>
+        <v>5.315018263812269</v>
       </c>
       <c r="P8" t="n">
-        <v>354.9235379664844</v>
+        <v>354.9148464796299</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33431,28 +33516,28 @@
         <v>0.0708</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7646556062313212</v>
+        <v>0.767561817177663</v>
       </c>
       <c r="J9" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K9" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5609559694153796</v>
+        <v>0.5633897879100818</v>
       </c>
       <c r="M9" t="n">
-        <v>3.865133961493122</v>
+        <v>3.87031342350984</v>
       </c>
       <c r="N9" t="n">
-        <v>24.88895603043274</v>
+        <v>24.90514529600338</v>
       </c>
       <c r="O9" t="n">
-        <v>4.988883244818698</v>
+        <v>4.990505515075941</v>
       </c>
       <c r="P9" t="n">
-        <v>347.7012869356141</v>
+        <v>347.6689936447787</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33509,28 +33594,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6455427023087118</v>
+        <v>0.6498659528049009</v>
       </c>
       <c r="J10" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K10" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4838739467073522</v>
+        <v>0.4867337678762858</v>
       </c>
       <c r="M10" t="n">
-        <v>3.800796078787387</v>
+        <v>3.811378099776523</v>
       </c>
       <c r="N10" t="n">
-        <v>24.1751467324311</v>
+        <v>24.29272426886739</v>
       </c>
       <c r="O10" t="n">
-        <v>4.916822829066662</v>
+        <v>4.928764984138257</v>
       </c>
       <c r="P10" t="n">
-        <v>348.3650023759797</v>
+        <v>348.3169631977489</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33587,28 +33672,28 @@
         <v>0.0702</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5228830905760975</v>
+        <v>0.5278004787500867</v>
       </c>
       <c r="J11" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K11" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4004094434307114</v>
+        <v>0.4037274216586991</v>
       </c>
       <c r="M11" t="n">
-        <v>3.601687896634181</v>
+        <v>3.616493717243162</v>
       </c>
       <c r="N11" t="n">
-        <v>22.26667095228242</v>
+        <v>22.44262149305326</v>
       </c>
       <c r="O11" t="n">
-        <v>4.718757352553999</v>
+        <v>4.737364403658775</v>
       </c>
       <c r="P11" t="n">
-        <v>352.0787015033249</v>
+        <v>352.0240603745889</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33665,28 +33750,28 @@
         <v>0.0683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7678725065867206</v>
+        <v>0.7704241060741878</v>
       </c>
       <c r="J12" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K12" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5833270649705786</v>
+        <v>0.5856272878108318</v>
       </c>
       <c r="M12" t="n">
-        <v>3.765030793095058</v>
+        <v>3.769007718024767</v>
       </c>
       <c r="N12" t="n">
-        <v>22.90640972274247</v>
+        <v>22.90904606934561</v>
       </c>
       <c r="O12" t="n">
-        <v>4.786064116029211</v>
+        <v>4.786339527169548</v>
       </c>
       <c r="P12" t="n">
-        <v>346.5082143419079</v>
+        <v>346.4798614295194</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33743,28 +33828,28 @@
         <v>0.0834</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8001284866358006</v>
+        <v>0.8036010662889003</v>
       </c>
       <c r="J13" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K13" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5689010706436095</v>
+        <v>0.5713080189937145</v>
       </c>
       <c r="M13" t="n">
-        <v>4.073480469723433</v>
+        <v>4.08003974343397</v>
       </c>
       <c r="N13" t="n">
-        <v>26.38488965703166</v>
+        <v>26.432210528958</v>
       </c>
       <c r="O13" t="n">
-        <v>5.136622397746564</v>
+        <v>5.141226558804621</v>
       </c>
       <c r="P13" t="n">
-        <v>340.1879662759888</v>
+        <v>340.1493795984361</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33821,28 +33906,28 @@
         <v>0.163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8885976095704227</v>
+        <v>0.8913757927014425</v>
       </c>
       <c r="J14" t="n">
+        <v>378</v>
+      </c>
+      <c r="K14" t="n">
         <v>377</v>
       </c>
-      <c r="K14" t="n">
-        <v>376</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.6161406895374748</v>
+        <v>0.6182771346948496</v>
       </c>
       <c r="M14" t="n">
-        <v>3.926937169377779</v>
+        <v>3.931216470115029</v>
       </c>
       <c r="N14" t="n">
-        <v>26.66426260852985</v>
+        <v>26.66820675201381</v>
       </c>
       <c r="O14" t="n">
-        <v>5.163745017768582</v>
+        <v>5.164126910912803</v>
       </c>
       <c r="P14" t="n">
-        <v>334.6375140603555</v>
+        <v>334.606552537793</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33899,28 +33984,28 @@
         <v>0.1423</v>
       </c>
       <c r="I15" t="n">
-        <v>0.774189538916196</v>
+        <v>0.7779205000017015</v>
       </c>
       <c r="J15" t="n">
+        <v>378</v>
+      </c>
+      <c r="K15" t="n">
         <v>377</v>
       </c>
-      <c r="K15" t="n">
-        <v>376</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.5538656539615561</v>
+        <v>0.5563644413520611</v>
       </c>
       <c r="M15" t="n">
-        <v>4.008990628029198</v>
+        <v>4.016328737275571</v>
       </c>
       <c r="N15" t="n">
-        <v>25.99045677434769</v>
+        <v>26.05469789873372</v>
       </c>
       <c r="O15" t="n">
-        <v>5.098083637441396</v>
+        <v>5.104380265882796</v>
       </c>
       <c r="P15" t="n">
-        <v>333.5346753666605</v>
+        <v>333.4929402714807</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33977,28 +34062,28 @@
         <v>0.0774</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6971718586933011</v>
+        <v>0.699859082689314</v>
       </c>
       <c r="J16" t="n">
+        <v>378</v>
+      </c>
+      <c r="K16" t="n">
         <v>377</v>
       </c>
-      <c r="K16" t="n">
-        <v>376</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.5169625695410888</v>
+        <v>0.5195821491733374</v>
       </c>
       <c r="M16" t="n">
-        <v>3.873662255828744</v>
+        <v>3.875810601115427</v>
       </c>
       <c r="N16" t="n">
-        <v>24.44890840814984</v>
+        <v>24.45314630894446</v>
       </c>
       <c r="O16" t="n">
-        <v>4.94458374467961</v>
+        <v>4.945012265803236</v>
       </c>
       <c r="P16" t="n">
-        <v>334.0096265084417</v>
+        <v>333.9795668142577</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34055,28 +34140,28 @@
         <v>0.1178</v>
       </c>
       <c r="I17" t="n">
-        <v>0.830894754836537</v>
+        <v>0.8324744203181511</v>
       </c>
       <c r="J17" t="n">
+        <v>378</v>
+      </c>
+      <c r="K17" t="n">
         <v>377</v>
       </c>
-      <c r="K17" t="n">
-        <v>376</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.6254384676548554</v>
+        <v>0.6273928598830522</v>
       </c>
       <c r="M17" t="n">
-        <v>3.887342029083664</v>
+        <v>3.884401585808043</v>
       </c>
       <c r="N17" t="n">
-        <v>22.25813177683208</v>
+        <v>22.22296602261729</v>
       </c>
       <c r="O17" t="n">
-        <v>4.717852453906553</v>
+        <v>4.714124099195659</v>
       </c>
       <c r="P17" t="n">
-        <v>332.285960111827</v>
+        <v>332.2682897347536</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34133,28 +34218,28 @@
         <v>0.1043</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8633156891214685</v>
+        <v>0.8635444727191727</v>
       </c>
       <c r="J18" t="n">
+        <v>378</v>
+      </c>
+      <c r="K18" t="n">
         <v>377</v>
       </c>
-      <c r="K18" t="n">
-        <v>376</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.6395119093721644</v>
+        <v>0.6409251175669075</v>
       </c>
       <c r="M18" t="n">
-        <v>3.868663324836334</v>
+        <v>3.859450067093557</v>
       </c>
       <c r="N18" t="n">
-        <v>22.61724186611479</v>
+        <v>22.55774996753592</v>
       </c>
       <c r="O18" t="n">
-        <v>4.755758810759309</v>
+        <v>4.749499970263808</v>
       </c>
       <c r="P18" t="n">
-        <v>325.4611509209825</v>
+        <v>325.4585917130447</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34211,28 +34296,28 @@
         <v>0.1026</v>
       </c>
       <c r="I19" t="n">
-        <v>1.003434553180453</v>
+        <v>1.005589568164067</v>
       </c>
       <c r="J19" t="n">
+        <v>378</v>
+      </c>
+      <c r="K19" t="n">
         <v>377</v>
       </c>
-      <c r="K19" t="n">
-        <v>376</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.7412530343760747</v>
+        <v>0.7427016119940082</v>
       </c>
       <c r="M19" t="n">
-        <v>3.556110817835802</v>
+        <v>3.557546206226967</v>
       </c>
       <c r="N19" t="n">
-        <v>18.92103875891987</v>
+        <v>18.91528300534542</v>
       </c>
       <c r="O19" t="n">
-        <v>4.349832038012488</v>
+        <v>4.349170381273354</v>
       </c>
       <c r="P19" t="n">
-        <v>319.5547533746009</v>
+        <v>319.5306470509503</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34289,28 +34374,28 @@
         <v>0.1406</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9639915565863505</v>
+        <v>0.9623465703058464</v>
       </c>
       <c r="J20" t="n">
+        <v>378</v>
+      </c>
+      <c r="K20" t="n">
         <v>377</v>
       </c>
-      <c r="K20" t="n">
-        <v>376</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.6565431046654439</v>
+        <v>0.656818251345056</v>
       </c>
       <c r="M20" t="n">
-        <v>4.136161313689817</v>
+        <v>4.131875305514368</v>
       </c>
       <c r="N20" t="n">
-        <v>26.17059193410717</v>
+        <v>26.12706358527907</v>
       </c>
       <c r="O20" t="n">
-        <v>5.115720079725548</v>
+        <v>5.111463937589609</v>
       </c>
       <c r="P20" t="n">
-        <v>323.1241272899424</v>
+        <v>323.1425283553551</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34367,28 +34452,28 @@
         <v>0.1091</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8881877442694535</v>
+        <v>0.8891638852128707</v>
       </c>
       <c r="J21" t="n">
+        <v>378</v>
+      </c>
+      <c r="K21" t="n">
         <v>377</v>
       </c>
-      <c r="K21" t="n">
-        <v>376</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.5953958612869017</v>
+        <v>0.5972031789596672</v>
       </c>
       <c r="M21" t="n">
-        <v>4.312773286512043</v>
+        <v>4.306159793348948</v>
       </c>
       <c r="N21" t="n">
-        <v>28.85972259782185</v>
+        <v>28.79228808482993</v>
       </c>
       <c r="O21" t="n">
-        <v>5.372124588821619</v>
+        <v>5.365844582619769</v>
       </c>
       <c r="P21" t="n">
-        <v>333.0568323482779</v>
+        <v>333.0459130879992</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34445,28 +34530,28 @@
         <v>0.1106</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8214817444580426</v>
+        <v>0.8232755231158598</v>
       </c>
       <c r="J22" t="n">
+        <v>378</v>
+      </c>
+      <c r="K22" t="n">
         <v>377</v>
       </c>
-      <c r="K22" t="n">
-        <v>376</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.4962127262553581</v>
+        <v>0.4985010346531586</v>
       </c>
       <c r="M22" t="n">
-        <v>4.9815239660876</v>
+        <v>4.976656837266288</v>
       </c>
       <c r="N22" t="n">
-        <v>36.88359273733705</v>
+        <v>36.81654330571931</v>
       </c>
       <c r="O22" t="n">
-        <v>6.073186374329134</v>
+        <v>6.06766374362648</v>
       </c>
       <c r="P22" t="n">
-        <v>332.027440908885</v>
+        <v>332.0073754294282</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34504,7 +34589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W378"/>
+  <dimension ref="A1:W379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78693,6 +78778,123 @@
         </is>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:25:59+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>-44.157594295912794,168.24376321537096</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>-44.15762978625482,168.24478223542403</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>-44.15734283056616,168.2455858927049</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-44.15698644078576,168.24633094618403</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>-44.15662131247815,168.24702950509402</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>-44.15615622204671,168.24763435451754</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>-44.1557371933289,168.24831658595647</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>-44.15531374531782,168.24899389574907</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>-44.154890083995625,168.24967097117545</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>-44.15446450420428,168.25032319871957</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>-44.154048055016446,168.25094009506327</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>-44.15355697777206,168.25147892055455</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>-44.153056487464724,168.25204414385774</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>-44.152544254357494,168.25258820536834</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>-44.152038598334165,168.25314413281282</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>-44.151523019804195,168.25365656191167</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>-44.15098755030769,168.25412201052913</t>
+        </is>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>-44.150387800898265,168.25444961791058</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>-44.14981092142215,168.2548493887623</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>-44.14917713161272,168.25504218053203</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>-44.148568600062895,168.25525693621128</t>
+        </is>
+      </c>
+      <c r="W379" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0455/nzd0455.xlsx
+++ b/data/nzd0455/nzd0455.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W379"/>
+  <dimension ref="A1:W382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28810,7 +28810,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>399.7</v>
+        <v>395.96</v>
       </c>
       <c r="C379" t="n">
         <v>358.09</v>
@@ -28875,6 +28875,231 @@
       <c r="W379" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-25 22:26:08+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>395.09</v>
+      </c>
+      <c r="C380" t="n">
+        <v>356.71</v>
+      </c>
+      <c r="D380" t="n">
+        <v>355.18</v>
+      </c>
+      <c r="E380" t="n">
+        <v>363.07</v>
+      </c>
+      <c r="F380" t="n">
+        <v>367.48</v>
+      </c>
+      <c r="G380" t="n">
+        <v>374.71</v>
+      </c>
+      <c r="H380" t="n">
+        <v>373.36</v>
+      </c>
+      <c r="I380" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="J380" t="n">
+        <v>373.44</v>
+      </c>
+      <c r="K380" t="n">
+        <v>375.08</v>
+      </c>
+      <c r="L380" t="n">
+        <v>372</v>
+      </c>
+      <c r="M380" t="n">
+        <v>367.04</v>
+      </c>
+      <c r="N380" t="n">
+        <v>362.62</v>
+      </c>
+      <c r="O380" t="n">
+        <v>360.42</v>
+      </c>
+      <c r="P380" t="n">
+        <v>356.81</v>
+      </c>
+      <c r="Q380" t="n">
+        <v>357.28</v>
+      </c>
+      <c r="R380" t="n">
+        <v>349.09</v>
+      </c>
+      <c r="S380" t="n">
+        <v>349.43</v>
+      </c>
+      <c r="T380" t="n">
+        <v>345.15</v>
+      </c>
+      <c r="U380" t="n">
+        <v>358.03</v>
+      </c>
+      <c r="V380" t="n">
+        <v>356.48</v>
+      </c>
+      <c r="W380" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:14+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>395.57</v>
+      </c>
+      <c r="C381" t="n">
+        <v>356.83</v>
+      </c>
+      <c r="D381" t="n">
+        <v>356.24</v>
+      </c>
+      <c r="E381" t="n">
+        <v>364.53</v>
+      </c>
+      <c r="F381" t="n">
+        <v>368.99</v>
+      </c>
+      <c r="G381" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="H381" t="n">
+        <v>374.47</v>
+      </c>
+      <c r="I381" t="n">
+        <v>373.39</v>
+      </c>
+      <c r="J381" t="n">
+        <v>373.55</v>
+      </c>
+      <c r="K381" t="n">
+        <v>376.63</v>
+      </c>
+      <c r="L381" t="n">
+        <v>373.15</v>
+      </c>
+      <c r="M381" t="n">
+        <v>366.97</v>
+      </c>
+      <c r="N381" t="n">
+        <v>363.04</v>
+      </c>
+      <c r="O381" t="n">
+        <v>360.55</v>
+      </c>
+      <c r="P381" t="n">
+        <v>357.39</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>357.69</v>
+      </c>
+      <c r="R381" t="n">
+        <v>349.17</v>
+      </c>
+      <c r="S381" t="n">
+        <v>351.01</v>
+      </c>
+      <c r="T381" t="n">
+        <v>346.92</v>
+      </c>
+      <c r="U381" t="n">
+        <v>359.27</v>
+      </c>
+      <c r="V381" t="n">
+        <v>357.59</v>
+      </c>
+      <c r="W381" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:22+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>396.63</v>
+      </c>
+      <c r="C382" t="n">
+        <v>356.3</v>
+      </c>
+      <c r="D382" t="n">
+        <v>355.32</v>
+      </c>
+      <c r="E382" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="F382" t="n">
+        <v>368.8</v>
+      </c>
+      <c r="G382" t="n">
+        <v>377.41</v>
+      </c>
+      <c r="H382" t="n">
+        <v>374.44</v>
+      </c>
+      <c r="I382" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="J382" t="n">
+        <v>374.33</v>
+      </c>
+      <c r="K382" t="n">
+        <v>376.66</v>
+      </c>
+      <c r="L382" t="n">
+        <v>372.85</v>
+      </c>
+      <c r="M382" t="n">
+        <v>365.68</v>
+      </c>
+      <c r="N382" t="n">
+        <v>363.51</v>
+      </c>
+      <c r="O382" t="n">
+        <v>360.55</v>
+      </c>
+      <c r="P382" t="n">
+        <v>355.49</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>357.43</v>
+      </c>
+      <c r="R382" t="n">
+        <v>350.02</v>
+      </c>
+      <c r="S382" t="n">
+        <v>351.25</v>
+      </c>
+      <c r="T382" t="n">
+        <v>349.02</v>
+      </c>
+      <c r="U382" t="n">
+        <v>359.92</v>
+      </c>
+      <c r="V382" t="n">
+        <v>356.99</v>
+      </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28889,7 +29114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B391"/>
+  <dimension ref="A1:B394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32802,6 +33027,36 @@
       </c>
       <c r="B391" t="n">
         <v>-0.23</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-07-25 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -32970,28 +33225,28 @@
         <v>0.0326</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2682588521546788</v>
+        <v>0.2838092352411558</v>
       </c>
       <c r="J2" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K2" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03194682539132732</v>
+        <v>0.03598326402619367</v>
       </c>
       <c r="M2" t="n">
-        <v>7.808497364462704</v>
+        <v>7.817126206622789</v>
       </c>
       <c r="N2" t="n">
-        <v>118.5459665455126</v>
+        <v>118.3459529167044</v>
       </c>
       <c r="O2" t="n">
-        <v>10.88788163719245</v>
+        <v>10.87869261063591</v>
       </c>
       <c r="P2" t="n">
-        <v>377.1763260577554</v>
+        <v>377.0023488417824</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33048,28 +33303,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4704732974091894</v>
+        <v>0.4744536720606722</v>
       </c>
       <c r="J3" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K3" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L3" t="n">
-        <v>0.265950214638611</v>
+        <v>0.272235659194266</v>
       </c>
       <c r="M3" t="n">
-        <v>4.434869385972249</v>
+        <v>4.421462882486346</v>
       </c>
       <c r="N3" t="n">
-        <v>33.3251847393078</v>
+        <v>33.11503332149852</v>
       </c>
       <c r="O3" t="n">
-        <v>5.772796959820067</v>
+        <v>5.754566301772751</v>
       </c>
       <c r="P3" t="n">
-        <v>341.313502885175</v>
+        <v>341.269125943143</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33126,28 +33381,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7308406736621839</v>
+        <v>0.7320187262927943</v>
       </c>
       <c r="J4" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K4" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4390873357104556</v>
+        <v>0.4439549208873215</v>
       </c>
       <c r="M4" t="n">
-        <v>4.748797513193799</v>
+        <v>4.717608219599517</v>
       </c>
       <c r="N4" t="n">
-        <v>37.21921329074004</v>
+        <v>36.9323821815408</v>
       </c>
       <c r="O4" t="n">
-        <v>6.100755141024759</v>
+        <v>6.077201838143998</v>
       </c>
       <c r="P4" t="n">
-        <v>335.0817238086846</v>
+        <v>335.0685864473467</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33204,28 +33459,28 @@
         <v>0.0653</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7493571185596206</v>
+        <v>0.7524442612322553</v>
       </c>
       <c r="J5" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K5" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5037116201637774</v>
+        <v>0.5096541867105978</v>
       </c>
       <c r="M5" t="n">
-        <v>4.190441990944308</v>
+        <v>4.174095353072961</v>
       </c>
       <c r="N5" t="n">
-        <v>30.17916695974646</v>
+        <v>29.97556342808046</v>
       </c>
       <c r="O5" t="n">
-        <v>5.493556858697874</v>
+        <v>5.474994376990761</v>
       </c>
       <c r="P5" t="n">
-        <v>341.6895060366518</v>
+        <v>341.6550750982481</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33282,28 +33537,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7909881419992849</v>
+        <v>0.7918470761567808</v>
       </c>
       <c r="J6" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K6" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4750762342178545</v>
+        <v>0.4797430608339479</v>
       </c>
       <c r="M6" t="n">
-        <v>4.507279818554358</v>
+        <v>4.478369321870193</v>
       </c>
       <c r="N6" t="n">
-        <v>37.70945992321698</v>
+        <v>37.41826323540988</v>
       </c>
       <c r="O6" t="n">
-        <v>6.140802872851154</v>
+        <v>6.117046937486248</v>
       </c>
       <c r="P6" t="n">
-        <v>346.5101404351685</v>
+        <v>346.5005519286861</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33360,28 +33615,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6340286327921212</v>
+        <v>0.6374417567735693</v>
       </c>
       <c r="J7" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K7" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4875717586585796</v>
+        <v>0.4939020110343569</v>
       </c>
       <c r="M7" t="n">
-        <v>3.644194277934217</v>
+        <v>3.636143206714758</v>
       </c>
       <c r="N7" t="n">
-        <v>23.04568880083293</v>
+        <v>22.91219236478508</v>
       </c>
       <c r="O7" t="n">
-        <v>4.800592546845954</v>
+        <v>4.786668190378887</v>
       </c>
       <c r="P7" t="n">
-        <v>356.9336042548483</v>
+        <v>356.8955265000926</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33438,28 +33693,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6436118469703471</v>
+        <v>0.6463684613128059</v>
       </c>
       <c r="J8" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K8" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4444023649242876</v>
+        <v>0.45040530265211</v>
       </c>
       <c r="M8" t="n">
-        <v>4.076028340683804</v>
+        <v>4.059859433033444</v>
       </c>
       <c r="N8" t="n">
-        <v>28.24941914465799</v>
+        <v>28.05376567163635</v>
       </c>
       <c r="O8" t="n">
-        <v>5.315018263812269</v>
+        <v>5.296580564065494</v>
       </c>
       <c r="P8" t="n">
-        <v>354.9148464796299</v>
+        <v>354.8841017437387</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33516,28 +33771,28 @@
         <v>0.0708</v>
       </c>
       <c r="I9" t="n">
-        <v>0.767561817177663</v>
+        <v>0.7747515020400436</v>
       </c>
       <c r="J9" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K9" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5633897879100818</v>
+        <v>0.5703874434176361</v>
       </c>
       <c r="M9" t="n">
-        <v>3.87031342350984</v>
+        <v>3.878039362350954</v>
       </c>
       <c r="N9" t="n">
-        <v>24.90514529600338</v>
+        <v>24.87847038443257</v>
       </c>
       <c r="O9" t="n">
-        <v>4.990505515075941</v>
+        <v>4.98783223298785</v>
       </c>
       <c r="P9" t="n">
-        <v>347.6689936447787</v>
+        <v>347.5888313042512</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33594,28 +33849,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6498659528049009</v>
+        <v>0.6619908352594954</v>
       </c>
       <c r="J10" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K10" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4867337678762858</v>
+        <v>0.4951972210594211</v>
       </c>
       <c r="M10" t="n">
-        <v>3.811378099776523</v>
+        <v>3.840631771494127</v>
       </c>
       <c r="N10" t="n">
-        <v>24.29272426886739</v>
+        <v>24.58325031752901</v>
       </c>
       <c r="O10" t="n">
-        <v>4.928764984138257</v>
+        <v>4.958149888570233</v>
       </c>
       <c r="P10" t="n">
-        <v>348.3169631977489</v>
+        <v>348.1817684071506</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33672,28 +33927,28 @@
         <v>0.0702</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5278004787500867</v>
+        <v>0.5428987299597278</v>
       </c>
       <c r="J11" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K11" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4037274216586991</v>
+        <v>0.4133922455953586</v>
       </c>
       <c r="M11" t="n">
-        <v>3.616493717243162</v>
+        <v>3.663993109993875</v>
       </c>
       <c r="N11" t="n">
-        <v>22.44262149305326</v>
+        <v>23.01520970023498</v>
       </c>
       <c r="O11" t="n">
-        <v>4.737364403658775</v>
+        <v>4.797416982109746</v>
       </c>
       <c r="P11" t="n">
-        <v>352.0240603745889</v>
+        <v>351.8557059321307</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33750,28 +34005,28 @@
         <v>0.0683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7704241060741878</v>
+        <v>0.7786792185468248</v>
       </c>
       <c r="J12" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K12" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5856272878108318</v>
+        <v>0.5924477144969149</v>
       </c>
       <c r="M12" t="n">
-        <v>3.769007718024767</v>
+        <v>3.784006656415583</v>
       </c>
       <c r="N12" t="n">
-        <v>22.90904606934561</v>
+        <v>22.95314944830898</v>
       </c>
       <c r="O12" t="n">
-        <v>4.786339527169548</v>
+        <v>4.790944525697305</v>
       </c>
       <c r="P12" t="n">
-        <v>346.4798614295194</v>
+        <v>346.3878118713667</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33828,28 +34083,28 @@
         <v>0.0834</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8036010662889003</v>
+        <v>0.8108312895035201</v>
       </c>
       <c r="J13" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K13" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5713080189937145</v>
+        <v>0.5781463690522417</v>
       </c>
       <c r="M13" t="n">
-        <v>4.08003974343397</v>
+        <v>4.084426781374882</v>
       </c>
       <c r="N13" t="n">
-        <v>26.432210528958</v>
+        <v>26.39835100636718</v>
       </c>
       <c r="O13" t="n">
-        <v>5.141226558804621</v>
+        <v>5.137932561484939</v>
       </c>
       <c r="P13" t="n">
-        <v>340.1493795984361</v>
+        <v>340.0687751805575</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33906,28 +34161,28 @@
         <v>0.163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8913757927014425</v>
+        <v>0.8981164691434206</v>
       </c>
       <c r="J14" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K14" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6182771346948496</v>
+        <v>0.6244304371989859</v>
       </c>
       <c r="M14" t="n">
-        <v>3.931216470115029</v>
+        <v>3.935469596089861</v>
       </c>
       <c r="N14" t="n">
-        <v>26.66820675201381</v>
+        <v>26.60651487044277</v>
       </c>
       <c r="O14" t="n">
-        <v>5.164126910912803</v>
+        <v>5.158150334222799</v>
       </c>
       <c r="P14" t="n">
-        <v>334.606552537793</v>
+        <v>334.5311685348397</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33984,28 +34239,28 @@
         <v>0.1423</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7779205000017015</v>
+        <v>0.7872193976401201</v>
       </c>
       <c r="J15" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K15" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5563644413520611</v>
+        <v>0.5637105899895454</v>
       </c>
       <c r="M15" t="n">
-        <v>4.016328737275571</v>
+        <v>4.029150977445422</v>
       </c>
       <c r="N15" t="n">
-        <v>26.05469789873372</v>
+        <v>26.12756398806682</v>
       </c>
       <c r="O15" t="n">
-        <v>5.104380265882796</v>
+        <v>5.111512886422847</v>
       </c>
       <c r="P15" t="n">
-        <v>333.4929402714807</v>
+        <v>333.3885694091572</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34062,28 +34317,28 @@
         <v>0.0774</v>
       </c>
       <c r="I16" t="n">
-        <v>0.699859082689314</v>
+        <v>0.7055639557436173</v>
       </c>
       <c r="J16" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K16" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5195821491733374</v>
+        <v>0.5266870567870051</v>
       </c>
       <c r="M16" t="n">
-        <v>3.875810601115427</v>
+        <v>3.872200587278602</v>
       </c>
       <c r="N16" t="n">
-        <v>24.45314630894446</v>
+        <v>24.37010364854096</v>
       </c>
       <c r="O16" t="n">
-        <v>4.945012265803236</v>
+        <v>4.936608516840378</v>
       </c>
       <c r="P16" t="n">
-        <v>333.9795668142577</v>
+        <v>333.9155445585559</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34140,28 +34395,28 @@
         <v>0.1178</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8324744203181511</v>
+        <v>0.8366866982527157</v>
       </c>
       <c r="J17" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K17" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6273928598830522</v>
+        <v>0.6330475561566133</v>
       </c>
       <c r="M17" t="n">
-        <v>3.884401585808043</v>
+        <v>3.873080191890786</v>
       </c>
       <c r="N17" t="n">
-        <v>22.22296602261729</v>
+        <v>22.1048740820045</v>
       </c>
       <c r="O17" t="n">
-        <v>4.714124099195659</v>
+        <v>4.701582082874285</v>
       </c>
       <c r="P17" t="n">
-        <v>332.2682897347536</v>
+        <v>332.2210100172629</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34218,28 +34473,28 @@
         <v>0.1043</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8635444727191727</v>
+        <v>0.8645554617078024</v>
       </c>
       <c r="J18" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K18" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6409251175669075</v>
+        <v>0.6452643231924831</v>
       </c>
       <c r="M18" t="n">
-        <v>3.859450067093557</v>
+        <v>3.833532911005708</v>
       </c>
       <c r="N18" t="n">
-        <v>22.55774996753592</v>
+        <v>22.38421153055267</v>
       </c>
       <c r="O18" t="n">
-        <v>4.749499970263808</v>
+        <v>4.731195570947439</v>
       </c>
       <c r="P18" t="n">
-        <v>325.4585917130447</v>
+        <v>325.447238097745</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34296,28 +34551,28 @@
         <v>0.1026</v>
       </c>
       <c r="I19" t="n">
-        <v>1.005589568164067</v>
+        <v>1.011600693244036</v>
       </c>
       <c r="J19" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K19" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7427016119940082</v>
+        <v>0.7469315513507194</v>
       </c>
       <c r="M19" t="n">
-        <v>3.557546206226967</v>
+        <v>3.559526581086427</v>
       </c>
       <c r="N19" t="n">
-        <v>18.91528300534542</v>
+        <v>18.88705751202826</v>
       </c>
       <c r="O19" t="n">
-        <v>4.349170381273354</v>
+        <v>4.345924241404613</v>
       </c>
       <c r="P19" t="n">
-        <v>319.5306470509503</v>
+        <v>319.4631632044652</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34374,28 +34629,28 @@
         <v>0.1406</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9623465703058464</v>
+        <v>0.9591088908909999</v>
       </c>
       <c r="J20" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K20" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L20" t="n">
-        <v>0.656818251345056</v>
+        <v>0.6586159429312225</v>
       </c>
       <c r="M20" t="n">
-        <v>4.131875305514368</v>
+        <v>4.112762267879204</v>
       </c>
       <c r="N20" t="n">
-        <v>26.12706358527907</v>
+        <v>25.97381232213086</v>
       </c>
       <c r="O20" t="n">
-        <v>5.111463937589609</v>
+        <v>5.096450953568655</v>
       </c>
       <c r="P20" t="n">
-        <v>323.1425283553551</v>
+        <v>323.1788372943712</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34452,28 +34707,28 @@
         <v>0.1091</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8891638852128707</v>
+        <v>0.892292526317231</v>
       </c>
       <c r="J21" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K21" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5972031789596672</v>
+        <v>0.6026117099268855</v>
       </c>
       <c r="M21" t="n">
-        <v>4.306159793348948</v>
+        <v>4.287386606343266</v>
       </c>
       <c r="N21" t="n">
-        <v>28.79228808482993</v>
+        <v>28.60097761840439</v>
       </c>
       <c r="O21" t="n">
-        <v>5.365844582619769</v>
+        <v>5.347988184205757</v>
       </c>
       <c r="P21" t="n">
-        <v>333.0459130879992</v>
+        <v>333.010782142757</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34530,28 +34785,28 @@
         <v>0.1106</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8232755231158598</v>
+        <v>0.8275843542274979</v>
       </c>
       <c r="J22" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K22" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4985010346531586</v>
+        <v>0.5048836934122767</v>
       </c>
       <c r="M22" t="n">
-        <v>4.976656837266288</v>
+        <v>4.957101663735233</v>
       </c>
       <c r="N22" t="n">
-        <v>36.81654330571931</v>
+        <v>36.58721035444847</v>
       </c>
       <c r="O22" t="n">
-        <v>6.06766374362648</v>
+        <v>6.048736260943146</v>
       </c>
       <c r="P22" t="n">
-        <v>332.0073754294282</v>
+        <v>331.9590081853278</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34589,7 +34844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W379"/>
+  <dimension ref="A1:W382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78786,7 +79041,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>-44.157594295912794,168.24376321537096</t>
+          <t>-44.15762458836781,168.24378344781752</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -78892,6 +79147,357 @@
       <c r="W379" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-25 22:26:08+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>-44.157631635008016,168.24378815429858</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>-44.15764096364395,168.2447897010233</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>-44.157351821050575,168.24559189770423</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>-44.156989371177055,168.2463331293986</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>-44.156617546789235,168.24702587544533</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>-44.156152717063655,168.24763044845096</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>-44.155739787005174,168.24831947644867</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>-44.15532012433231,168.24900100480352</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>-44.154894430119,168.2496758147106</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>-44.15446815172913,168.25032764531667</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>-44.15404859500201,168.25094093152606</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>-44.15356449226584,168.2514924679169</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>-44.15306339856078,168.25205660342604</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>-44.15255012326844,168.2525987860663</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>-44.152044576906874,168.25315491123615</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>-44.15152490469009,168.25366066628536</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>-44.15098774835723,168.2541225707676</t>
+        </is>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>-44.15039252617083,168.25446377350914</t>
+        </is>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>-44.14981390776967,168.25485833503228</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>-44.14917961970846,168.25505154924213</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>-44.148571207018506,168.25526992142795</t>
+        </is>
+      </c>
+      <c r="W380" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:14+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>-44.15762774720655,168.24378555761925</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>-44.15763999169709,168.24478905184068</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-44.15734323554294,168.2455861632003</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-44.15697780801116,168.24632451455312</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>-44.15660639739598,168.2470151288412</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>-44.15613869713027,168.24761482418924</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>-44.155732005976155,168.24831080497273</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>-44.15531718017183,168.24899772370128</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>-44.154893659032616,168.24967495537368</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>-44.15445768198146,168.25031488193758</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>-44.15404169518608,168.25093024339154</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>-44.15356487621804,168.251493160118</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>-44.15306109486224,168.25205245023628</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>-44.15254941022324,168.25259750056085</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>-44.15204139564811,168.25314917592803</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>-44.15152292314338,168.25365635143095</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>-44.15098743147796,168.25412167438608</t>
+        </is>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>-44.15038655342602,168.25444588083295</t>
+        </is>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>-44.149807216838255,168.25483829085906</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>-44.14917576315974,168.25503702774185</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>-44.14856852764744,168.25525657551086</t>
+        </is>
+      </c>
+      <c r="W381" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-18 22:26:22+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>-44.15761916164479,168.24377982328687</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>-44.157644284462386,168.2447919190642</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-44.15735068711562,168.24559114031683</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-44.15698042160351,168.24632646174393</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>-44.156607800299824,168.2470164810627</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>-44.15613379015314,168.24760935569938</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>-44.15573221627423,168.2483110393369</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>-44.15532075522384,168.2490017078969</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>-44.15488819132894,168.24966886189418</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>-44.154457479341175,168.25031463490447</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>-44.15404349513814,168.2509330316003</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>-44.15357195190786,168.25150591639687</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>-44.153058516913696,168.25204780261956</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>-44.15254941022324,168.25259750056085</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>-44.15205181701206,168.25316796400858</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>-44.15152417973399,168.25365908768006</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>-44.150984064635445,168.25411215033301</t>
+        </is>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>-44.15038564617341,168.2544431629584</t>
+        </is>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>-44.14979927844071,168.25481450964276</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>-44.14917374158109,168.25502941566592</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>-44.14856997595631,168.25526378951992</t>
+        </is>
+      </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0455/nzd0455.xlsx
+++ b/data/nzd0455/nzd0455.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W382"/>
+  <dimension ref="A1:W384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29098,6 +29098,156 @@
         <v>356.99</v>
       </c>
       <c r="W382" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:24+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>391.76</v>
+      </c>
+      <c r="C383" t="n">
+        <v>353.74</v>
+      </c>
+      <c r="D383" t="n">
+        <v>354.37</v>
+      </c>
+      <c r="E383" t="n">
+        <v>364.01</v>
+      </c>
+      <c r="F383" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="G383" t="n">
+        <v>378.35</v>
+      </c>
+      <c r="H383" t="n">
+        <v>374.48</v>
+      </c>
+      <c r="I383" t="n">
+        <v>372.2</v>
+      </c>
+      <c r="J383" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="K383" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="L383" t="n">
+        <v>371.33</v>
+      </c>
+      <c r="M383" t="n">
+        <v>363.69</v>
+      </c>
+      <c r="N383" t="n">
+        <v>360.65</v>
+      </c>
+      <c r="O383" t="n">
+        <v>357.98</v>
+      </c>
+      <c r="P383" t="n">
+        <v>355.27</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>355.68</v>
+      </c>
+      <c r="R383" t="n">
+        <v>348.9</v>
+      </c>
+      <c r="S383" t="n">
+        <v>348.42</v>
+      </c>
+      <c r="T383" t="n">
+        <v>349.27</v>
+      </c>
+      <c r="U383" t="n">
+        <v>358.77</v>
+      </c>
+      <c r="V383" t="n">
+        <v>355.68</v>
+      </c>
+      <c r="W383" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:26:33+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>387.03</v>
+      </c>
+      <c r="C384" t="n">
+        <v>351.4</v>
+      </c>
+      <c r="D384" t="n">
+        <v>351.37</v>
+      </c>
+      <c r="E384" t="n">
+        <v>362.04</v>
+      </c>
+      <c r="F384" t="n">
+        <v>368.91</v>
+      </c>
+      <c r="G384" t="n">
+        <v>376.81</v>
+      </c>
+      <c r="H384" t="n">
+        <v>372.2</v>
+      </c>
+      <c r="I384" t="n">
+        <v>370.06</v>
+      </c>
+      <c r="J384" t="n">
+        <v>372.29</v>
+      </c>
+      <c r="K384" t="n">
+        <v>374.52</v>
+      </c>
+      <c r="L384" t="n">
+        <v>368.76</v>
+      </c>
+      <c r="M384" t="n">
+        <v>361.62</v>
+      </c>
+      <c r="N384" t="n">
+        <v>358.3</v>
+      </c>
+      <c r="O384" t="n">
+        <v>356.43</v>
+      </c>
+      <c r="P384" t="n">
+        <v>353.04</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>353.96</v>
+      </c>
+      <c r="R384" t="n">
+        <v>348.06</v>
+      </c>
+      <c r="S384" t="n">
+        <v>346.91</v>
+      </c>
+      <c r="T384" t="n">
+        <v>347.96</v>
+      </c>
+      <c r="U384" t="n">
+        <v>357.28</v>
+      </c>
+      <c r="V384" t="n">
+        <v>353.41</v>
+      </c>
+      <c r="W384" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29114,7 +29264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B394"/>
+  <dimension ref="A1:B396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33057,6 +33207,26 @@
       </c>
       <c r="B394" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -33225,28 +33395,28 @@
         <v>0.0326</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2838092352411558</v>
+        <v>0.2885943505710786</v>
       </c>
       <c r="J2" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K2" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03598326402619367</v>
+        <v>0.03751491266014217</v>
       </c>
       <c r="M2" t="n">
-        <v>7.817126206622789</v>
+        <v>7.798170608522144</v>
       </c>
       <c r="N2" t="n">
-        <v>118.3459529167044</v>
+        <v>117.8694637952186</v>
       </c>
       <c r="O2" t="n">
-        <v>10.87869261063591</v>
+        <v>10.85677041275252</v>
       </c>
       <c r="P2" t="n">
-        <v>377.0023488417824</v>
+        <v>376.948611066298</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33303,28 +33473,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4744536720606722</v>
+        <v>0.4728695657795589</v>
       </c>
       <c r="J3" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K3" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L3" t="n">
-        <v>0.272235659194266</v>
+        <v>0.2729806558605068</v>
       </c>
       <c r="M3" t="n">
-        <v>4.421462882486346</v>
+        <v>4.405906914659116</v>
       </c>
       <c r="N3" t="n">
-        <v>33.11503332149852</v>
+        <v>32.96182207240232</v>
       </c>
       <c r="O3" t="n">
-        <v>5.754566301772751</v>
+        <v>5.741238722819521</v>
       </c>
       <c r="P3" t="n">
-        <v>341.269125943143</v>
+        <v>341.286874104671</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33381,28 +33551,28 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7320187262927943</v>
+        <v>0.7299490610173512</v>
       </c>
       <c r="J4" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K4" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4439549208873215</v>
+        <v>0.4450607739440133</v>
       </c>
       <c r="M4" t="n">
-        <v>4.717608219599517</v>
+        <v>4.70320099816471</v>
       </c>
       <c r="N4" t="n">
-        <v>36.9323821815408</v>
+        <v>36.77270723118394</v>
       </c>
       <c r="O4" t="n">
-        <v>6.077201838143998</v>
+        <v>6.064050398140169</v>
       </c>
       <c r="P4" t="n">
-        <v>335.0685864473467</v>
+        <v>335.0917746049261</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33459,28 +33629,28 @@
         <v>0.0653</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7524442612322553</v>
+        <v>0.7534338336730121</v>
       </c>
       <c r="J5" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K5" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5096541867105978</v>
+        <v>0.5129862958031302</v>
       </c>
       <c r="M5" t="n">
-        <v>4.174095353072961</v>
+        <v>4.15777794607677</v>
       </c>
       <c r="N5" t="n">
-        <v>29.97556342808046</v>
+        <v>29.82909288825408</v>
       </c>
       <c r="O5" t="n">
-        <v>5.474994376990761</v>
+        <v>5.461601677919591</v>
       </c>
       <c r="P5" t="n">
-        <v>341.6550750982481</v>
+        <v>341.6439972238239</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33537,28 +33707,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7918470761567808</v>
+        <v>0.7931626181591079</v>
       </c>
       <c r="J6" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K6" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4797430608339479</v>
+        <v>0.4832668802863758</v>
       </c>
       <c r="M6" t="n">
-        <v>4.478369321870193</v>
+        <v>4.462152748220472</v>
       </c>
       <c r="N6" t="n">
-        <v>37.41826323540988</v>
+        <v>37.23215133948644</v>
       </c>
       <c r="O6" t="n">
-        <v>6.117046937486248</v>
+        <v>6.101815413422996</v>
       </c>
       <c r="P6" t="n">
-        <v>346.5005519286861</v>
+        <v>346.4858198040111</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33615,28 +33785,28 @@
         <v>0.0478</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6374417567735693</v>
+        <v>0.6408964327269917</v>
       </c>
       <c r="J7" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K7" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4939020110343569</v>
+        <v>0.4986788179176527</v>
       </c>
       <c r="M7" t="n">
-        <v>3.636143206714758</v>
+        <v>3.638389770480208</v>
       </c>
       <c r="N7" t="n">
-        <v>22.91219236478508</v>
+        <v>22.85521086678478</v>
       </c>
       <c r="O7" t="n">
-        <v>4.786668190378887</v>
+        <v>4.780712380679764</v>
       </c>
       <c r="P7" t="n">
-        <v>356.8955265000926</v>
+        <v>356.8568384324839</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33693,28 +33863,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6463684613128059</v>
+        <v>0.647315028337808</v>
       </c>
       <c r="J8" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K8" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L8" t="n">
-        <v>0.45040530265211</v>
+        <v>0.4537653890357434</v>
       </c>
       <c r="M8" t="n">
-        <v>4.059859433033444</v>
+        <v>4.045243377687056</v>
       </c>
       <c r="N8" t="n">
-        <v>28.05376567163635</v>
+        <v>27.91859880582128</v>
       </c>
       <c r="O8" t="n">
-        <v>5.296580564065494</v>
+        <v>5.283805333831034</v>
       </c>
       <c r="P8" t="n">
-        <v>354.8841017437387</v>
+        <v>354.8735063276025</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33771,28 +33941,28 @@
         <v>0.0708</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7747515020400436</v>
+        <v>0.7773287240872989</v>
       </c>
       <c r="J9" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K9" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5703874434176361</v>
+        <v>0.5743287558290713</v>
       </c>
       <c r="M9" t="n">
-        <v>3.878039362350954</v>
+        <v>3.871664089187034</v>
       </c>
       <c r="N9" t="n">
-        <v>24.87847038443257</v>
+        <v>24.78777664018451</v>
       </c>
       <c r="O9" t="n">
-        <v>4.98783223298785</v>
+        <v>4.978732433078174</v>
       </c>
       <c r="P9" t="n">
-        <v>347.5888313042512</v>
+        <v>347.5599722842953</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33849,28 +34019,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6619908352594954</v>
+        <v>0.6690125902341512</v>
       </c>
       <c r="J10" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K10" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4951972210594211</v>
+        <v>0.500702848421605</v>
       </c>
       <c r="M10" t="n">
-        <v>3.840631771494127</v>
+        <v>3.856153408099187</v>
       </c>
       <c r="N10" t="n">
-        <v>24.58325031752901</v>
+        <v>24.70369964988065</v>
       </c>
       <c r="O10" t="n">
-        <v>4.958149888570233</v>
+        <v>4.970281646937189</v>
       </c>
       <c r="P10" t="n">
-        <v>348.1817684071506</v>
+        <v>348.1031291500948</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33927,28 +34097,28 @@
         <v>0.0702</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5428987299597278</v>
+        <v>0.5520845164058454</v>
       </c>
       <c r="J11" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K11" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4133922455953586</v>
+        <v>0.419741011854454</v>
       </c>
       <c r="M11" t="n">
-        <v>3.663993109993875</v>
+        <v>3.691949514269609</v>
       </c>
       <c r="N11" t="n">
-        <v>23.01520970023498</v>
+        <v>23.32201100531667</v>
       </c>
       <c r="O11" t="n">
-        <v>4.797416982109746</v>
+        <v>4.829286800896865</v>
       </c>
       <c r="P11" t="n">
-        <v>351.8557059321307</v>
+        <v>351.7528314374291</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34005,28 +34175,28 @@
         <v>0.0683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7786792185468248</v>
+        <v>0.781266486619013</v>
       </c>
       <c r="J12" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K12" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5924477144969149</v>
+        <v>0.5962649854767282</v>
       </c>
       <c r="M12" t="n">
-        <v>3.784006656415583</v>
+        <v>3.778148789454681</v>
       </c>
       <c r="N12" t="n">
-        <v>22.95314944830898</v>
+        <v>22.87546281343826</v>
       </c>
       <c r="O12" t="n">
-        <v>4.790944525697305</v>
+        <v>4.782830000474433</v>
       </c>
       <c r="P12" t="n">
-        <v>346.3878118713667</v>
+        <v>346.3588414880555</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34083,28 +34253,28 @@
         <v>0.0834</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8108312895035201</v>
+        <v>0.8114483801846801</v>
       </c>
       <c r="J13" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K13" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5781463690522417</v>
+        <v>0.5811371497235732</v>
       </c>
       <c r="M13" t="n">
-        <v>4.084426781374882</v>
+        <v>4.068561524238874</v>
       </c>
       <c r="N13" t="n">
-        <v>26.39835100636718</v>
+        <v>26.26814411369897</v>
       </c>
       <c r="O13" t="n">
-        <v>5.137932561484939</v>
+        <v>5.125245761297595</v>
       </c>
       <c r="P13" t="n">
-        <v>340.0687751805575</v>
+        <v>340.0618693669325</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34161,28 +34331,28 @@
         <v>0.163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8981164691434206</v>
+        <v>0.8987293135875356</v>
       </c>
       <c r="J14" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K14" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6244304371989859</v>
+        <v>0.6272556047722978</v>
       </c>
       <c r="M14" t="n">
-        <v>3.935469596089861</v>
+        <v>3.921183634116399</v>
       </c>
       <c r="N14" t="n">
-        <v>26.60651487044277</v>
+        <v>26.47646338728583</v>
       </c>
       <c r="O14" t="n">
-        <v>5.158150334222799</v>
+        <v>5.145528484741468</v>
       </c>
       <c r="P14" t="n">
-        <v>334.5311685348397</v>
+        <v>334.524290895004</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34239,28 +34409,28 @@
         <v>0.1423</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7872193976401201</v>
+        <v>0.7897615884853548</v>
       </c>
       <c r="J15" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K15" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5637105899895454</v>
+        <v>0.5676908645123946</v>
       </c>
       <c r="M15" t="n">
-        <v>4.029150977445422</v>
+        <v>4.02014785101809</v>
       </c>
       <c r="N15" t="n">
-        <v>26.12756398806682</v>
+        <v>26.02573563207102</v>
       </c>
       <c r="O15" t="n">
-        <v>5.111512886422847</v>
+        <v>5.10154247576858</v>
       </c>
       <c r="P15" t="n">
-        <v>333.3885694091572</v>
+        <v>333.3599127088303</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34317,28 +34487,28 @@
         <v>0.0774</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7055639557436173</v>
+        <v>0.706708510011227</v>
       </c>
       <c r="J16" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K16" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5266870567870051</v>
+        <v>0.5301259761926866</v>
       </c>
       <c r="M16" t="n">
-        <v>3.872200587278602</v>
+        <v>3.857444504573257</v>
       </c>
       <c r="N16" t="n">
-        <v>24.37010364854096</v>
+        <v>24.2555700171596</v>
       </c>
       <c r="O16" t="n">
-        <v>4.936608516840378</v>
+        <v>4.924994417982583</v>
       </c>
       <c r="P16" t="n">
-        <v>333.9155445585559</v>
+        <v>333.9026467621082</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34395,28 +34565,28 @@
         <v>0.1178</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8366866982527157</v>
+        <v>0.8366058431316827</v>
       </c>
       <c r="J17" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K17" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6330475561566133</v>
+        <v>0.6355350134666107</v>
       </c>
       <c r="M17" t="n">
-        <v>3.873080191890786</v>
+        <v>3.857382169711619</v>
       </c>
       <c r="N17" t="n">
-        <v>22.1048740820045</v>
+        <v>21.99310813999386</v>
       </c>
       <c r="O17" t="n">
-        <v>4.701582082874285</v>
+        <v>4.689681027532028</v>
       </c>
       <c r="P17" t="n">
-        <v>332.2210100172629</v>
+        <v>332.2219262227086</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -34473,28 +34643,28 @@
         <v>0.1043</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8645554617078024</v>
+        <v>0.864146082547641</v>
       </c>
       <c r="J18" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K18" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6452643231924831</v>
+        <v>0.6475659118010586</v>
       </c>
       <c r="M18" t="n">
-        <v>3.833532911005708</v>
+        <v>3.815945606669954</v>
       </c>
       <c r="N18" t="n">
-        <v>22.38421153055267</v>
+        <v>22.26879674769568</v>
       </c>
       <c r="O18" t="n">
-        <v>4.731195570947439</v>
+        <v>4.718982596672261</v>
       </c>
       <c r="P18" t="n">
-        <v>325.447238097745</v>
+        <v>325.4518557646879</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -34551,28 +34721,28 @@
         <v>0.1026</v>
       </c>
       <c r="I19" t="n">
-        <v>1.011600693244036</v>
+        <v>1.012404577083199</v>
       </c>
       <c r="J19" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K19" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7469315513507194</v>
+        <v>0.7492596111224079</v>
       </c>
       <c r="M19" t="n">
-        <v>3.559526581086427</v>
+        <v>3.544857540936028</v>
       </c>
       <c r="N19" t="n">
-        <v>18.88705751202826</v>
+        <v>18.7944085960653</v>
       </c>
       <c r="O19" t="n">
-        <v>4.345924241404613</v>
+        <v>4.335251849208452</v>
       </c>
       <c r="P19" t="n">
-        <v>319.4631632044652</v>
+        <v>319.4541042327373</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -34629,28 +34799,28 @@
         <v>0.1406</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9591088908909999</v>
+        <v>0.9585321508286493</v>
       </c>
       <c r="J20" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K20" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6586159429312225</v>
+        <v>0.6608027771390009</v>
       </c>
       <c r="M20" t="n">
-        <v>4.112762267879204</v>
+        <v>4.094218844749484</v>
       </c>
       <c r="N20" t="n">
-        <v>25.97381232213086</v>
+        <v>25.84177192546274</v>
       </c>
       <c r="O20" t="n">
-        <v>5.096450953568655</v>
+        <v>5.083480296554983</v>
       </c>
       <c r="P20" t="n">
-        <v>323.1788372943712</v>
+        <v>323.1853430738833</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -34707,28 +34877,28 @@
         <v>0.1091</v>
       </c>
       <c r="I21" t="n">
-        <v>0.892292526317231</v>
+        <v>0.8931438630555413</v>
       </c>
       <c r="J21" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K21" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6026117099268855</v>
+        <v>0.6056668411445991</v>
       </c>
       <c r="M21" t="n">
-        <v>4.287386606343266</v>
+        <v>4.269028355576938</v>
       </c>
       <c r="N21" t="n">
-        <v>28.60097761840439</v>
+        <v>28.45776763311824</v>
       </c>
       <c r="O21" t="n">
-        <v>5.347988184205757</v>
+        <v>5.334582236044191</v>
       </c>
       <c r="P21" t="n">
-        <v>333.010782142757</v>
+        <v>333.0011881229453</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34785,28 +34955,28 @@
         <v>0.1106</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8275843542274979</v>
+        <v>0.8277433607238133</v>
       </c>
       <c r="J22" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K22" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5048836934122767</v>
+        <v>0.5077054728279875</v>
       </c>
       <c r="M22" t="n">
-        <v>4.957101663735233</v>
+        <v>4.937065080382591</v>
       </c>
       <c r="N22" t="n">
-        <v>36.58721035444847</v>
+        <v>36.40265558616979</v>
       </c>
       <c r="O22" t="n">
-        <v>6.048736260943146</v>
+        <v>6.033461327146283</v>
       </c>
       <c r="P22" t="n">
-        <v>331.9590081853278</v>
+        <v>331.957221661675</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34844,7 +35014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W382"/>
+  <dimension ref="A1:W384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79501,6 +79671,240 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:26:24+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>-44.15765860662948,168.2438061687704</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>-44.15766501932797,168.24480576830052</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-44.15735838167416,168.24559627973187</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-44.15698192639907,168.2463275828539</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>-44.15660189333623,168.24701078749897</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>-44.156127200783516,168.24760201230006</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>-44.15573193587678,168.24831072685132</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>-44.15532552195968,168.24900702015847</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>-44.15489190656351,168.24967300233527</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>-44.15445714160736,168.25031422318264</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>-44.15405261489436,168.2509471585273</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>-44.15358286711671,168.25152559469365</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>-44.153074204002145,168.2520760838681</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>-44.152563506576044,168.25262291402112</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>-44.152053023696126,168.253170139471</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>-44.15153263755386,168.25367750474433</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>-44.150988500945445,168.25412469967378</t>
+        </is>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>-44.15039634418986,168.25447521123453</t>
+        </is>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>-44.14979833339307,168.25481167854602</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>-44.14917731821993,168.25504288318527</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>-44.1485731380958,168.25527954010775</t>
+        </is>
+      </c>
+      <c r="W383" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-19 22:26:33+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>-44.15769691766758,168.24383175692094</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>-44.1576839722899,168.2448184273762</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-44.15738268027895,168.24561250947195</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-44.15699752875269,168.24633920699702</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>-44.156606988092335,168.24701569819763</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>-44.156137996133545,168.24761404297635</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>-44.155747918530416,168.24832853853408</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>-44.155340523156354,168.2490237381637</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>-44.154902491476385,168.24968479868903</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>-44.15447193434734,168.25033225660314</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>-44.154068034478556,168.25097104419683</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>-44.15359422112466,168.25154606408557</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>-44.153087093737874,168.2520993219684</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>-44.15257200826492,168.2526382412113</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>-44.152065255082455,168.25319219075402</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>-44.15154095037986,168.25369560609278</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>-44.15099182817709,168.25413411168066</t>
+        </is>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>-44.15040205231529,168.2544923112031</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>-44.14980328544195,168.25482651349395</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>-44.149181952297546,168.2550603324086</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>-44.14857861752337,168.25530683311553</t>
+        </is>
+      </c>
+      <c r="W384" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
